--- a/services/compset/MASTER/COMPSET_MASTER.xlsx
+++ b/services/compset/MASTER/COMPSET_MASTER.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -821,7 +821,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -942,7 +942,7 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1184,7 +1184,7 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1305,7 +1305,7 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1426,7 +1426,7 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1547,7 +1547,7 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1668,7 +1668,7 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1789,7 +1789,7 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1910,7 +1910,7 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2031,7 +2031,7 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>upper_upscale</t>
+          <t>upscale</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2273,7 +2273,7 @@
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>upper_midscale</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2515,7 +2515,7 @@
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2636,7 +2636,7 @@
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>upper_midscale</t>
+          <t>upscale</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -2757,7 +2757,7 @@
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -2878,7 +2878,7 @@
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -2999,7 +2999,7 @@
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3120,7 +3120,7 @@
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3241,7 +3241,7 @@
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3362,7 +3362,7 @@
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -3483,7 +3483,7 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -3725,7 +3725,7 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -3846,7 +3846,7 @@
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -3967,7 +3967,7 @@
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -4088,7 +4088,7 @@
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4209,7 +4209,7 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -4330,7 +4330,7 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -4572,7 +4572,7 @@
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -4693,7 +4693,7 @@
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -4814,7 +4814,7 @@
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -4935,7 +4935,7 @@
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5056,7 +5056,7 @@
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -5177,7 +5177,7 @@
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -5298,7 +5298,7 @@
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -5419,7 +5419,7 @@
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -5540,7 +5540,7 @@
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -5661,7 +5661,7 @@
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -5782,7 +5782,7 @@
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -5903,7 +5903,7 @@
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -6024,7 +6024,7 @@
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -6145,7 +6145,7 @@
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -6266,7 +6266,7 @@
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -6387,7 +6387,7 @@
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -6508,7 +6508,7 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -6629,7 +6629,7 @@
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -6750,7 +6750,7 @@
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -6871,7 +6871,7 @@
       <c r="AM52" t="inlineStr"/>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -6992,7 +6992,7 @@
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -7113,7 +7113,7 @@
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -7234,7 +7234,7 @@
       <c r="AM55" t="inlineStr"/>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -7355,7 +7355,7 @@
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -7476,7 +7476,7 @@
       <c r="AM57" t="inlineStr"/>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -7597,7 +7597,7 @@
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -7718,7 +7718,7 @@
       <c r="AM59" t="inlineStr"/>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -7839,7 +7839,7 @@
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -7960,7 +7960,7 @@
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -8081,7 +8081,7 @@
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -8202,7 +8202,7 @@
       <c r="AM63" t="inlineStr"/>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -8323,7 +8323,7 @@
       <c r="AM64" t="inlineStr"/>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -8444,7 +8444,7 @@
       <c r="AM65" t="inlineStr"/>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -8565,7 +8565,7 @@
       <c r="AM66" t="inlineStr"/>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -8686,7 +8686,7 @@
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -8807,7 +8807,7 @@
       <c r="AM68" t="inlineStr"/>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -8928,7 +8928,7 @@
       <c r="AM69" t="inlineStr"/>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -9049,7 +9049,7 @@
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -9170,7 +9170,7 @@
       <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -9291,7 +9291,7 @@
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -9412,7 +9412,7 @@
       <c r="AM73" t="inlineStr"/>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -9533,7 +9533,7 @@
       <c r="AM74" t="inlineStr"/>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -9654,7 +9654,7 @@
       <c r="AM75" t="inlineStr"/>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -9775,7 +9775,7 @@
       <c r="AM76" t="inlineStr"/>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -9896,7 +9896,7 @@
       <c r="AM77" t="inlineStr"/>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -10017,7 +10017,7 @@
       <c r="AM78" t="inlineStr"/>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -10138,7 +10138,7 @@
       <c r="AM79" t="inlineStr"/>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -10259,7 +10259,7 @@
       <c r="AM80" t="inlineStr"/>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -10380,7 +10380,7 @@
       <c r="AM81" t="inlineStr"/>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -10501,7 +10501,7 @@
       <c r="AM82" t="inlineStr"/>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -10622,7 +10622,7 @@
       <c r="AM83" t="inlineStr"/>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -10743,7 +10743,7 @@
       <c r="AM84" t="inlineStr"/>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -10864,7 +10864,7 @@
       <c r="AM85" t="inlineStr"/>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -10985,7 +10985,7 @@
       <c r="AM86" t="inlineStr"/>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -11106,7 +11106,7 @@
       <c r="AM87" t="inlineStr"/>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -11227,7 +11227,7 @@
       <c r="AM88" t="inlineStr"/>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -11348,7 +11348,7 @@
       <c r="AM89" t="inlineStr"/>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>upper_midscale</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -11469,7 +11469,7 @@
       <c r="AM90" t="inlineStr"/>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -11590,7 +11590,7 @@
       <c r="AM91" t="inlineStr"/>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -11711,7 +11711,7 @@
       <c r="AM92" t="inlineStr"/>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -11832,7 +11832,7 @@
       <c r="AM93" t="inlineStr"/>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -11953,7 +11953,7 @@
       <c r="AM94" t="inlineStr"/>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -12074,7 +12074,7 @@
       <c r="AM95" t="inlineStr"/>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -12195,7 +12195,7 @@
       <c r="AM96" t="inlineStr"/>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -12316,7 +12316,7 @@
       <c r="AM97" t="inlineStr"/>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -12437,7 +12437,7 @@
       <c r="AM98" t="inlineStr"/>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -12558,7 +12558,7 @@
       <c r="AM99" t="inlineStr"/>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -12679,7 +12679,7 @@
       <c r="AM100" t="inlineStr"/>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -12800,7 +12800,7 @@
       <c r="AM101" t="inlineStr"/>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -12921,7 +12921,7 @@
       <c r="AM102" t="inlineStr"/>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -13042,7 +13042,7 @@
       <c r="AM103" t="inlineStr"/>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -13163,7 +13163,7 @@
       <c r="AM104" t="inlineStr"/>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -13284,7 +13284,7 @@
       <c r="AM105" t="inlineStr"/>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -13405,7 +13405,7 @@
       <c r="AM106" t="inlineStr"/>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -13526,7 +13526,7 @@
       <c r="AM107" t="inlineStr"/>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -13647,7 +13647,7 @@
       <c r="AM108" t="inlineStr"/>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -13768,7 +13768,7 @@
       <c r="AM109" t="inlineStr"/>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -13889,7 +13889,7 @@
       <c r="AM110" t="inlineStr"/>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -14010,7 +14010,7 @@
       <c r="AM111" t="inlineStr"/>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -14131,7 +14131,7 @@
       <c r="AM112" t="inlineStr"/>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -14252,7 +14252,7 @@
       <c r="AM113" t="inlineStr"/>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -14373,7 +14373,7 @@
       <c r="AM114" t="inlineStr"/>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -14494,7 +14494,7 @@
       <c r="AM115" t="inlineStr"/>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -14615,7 +14615,7 @@
       <c r="AM116" t="inlineStr"/>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -14736,7 +14736,7 @@
       <c r="AM117" t="inlineStr"/>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -14857,7 +14857,7 @@
       <c r="AM118" t="inlineStr"/>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -14978,7 +14978,7 @@
       <c r="AM119" t="inlineStr"/>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -15099,7 +15099,7 @@
       <c r="AM120" t="inlineStr"/>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -15220,7 +15220,7 @@
       <c r="AM121" t="inlineStr"/>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -15341,7 +15341,7 @@
       <c r="AM122" t="inlineStr"/>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -15462,7 +15462,7 @@
       <c r="AM123" t="inlineStr"/>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -15583,7 +15583,7 @@
       <c r="AM124" t="inlineStr"/>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -15704,7 +15704,7 @@
       <c r="AM125" t="inlineStr"/>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -15825,7 +15825,7 @@
       <c r="AM126" t="inlineStr"/>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -15946,7 +15946,7 @@
       <c r="AM127" t="inlineStr"/>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -16067,7 +16067,7 @@
       <c r="AM128" t="inlineStr"/>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16172,7 +16172,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -16188,7 +16188,7 @@
       <c r="AM129" t="inlineStr"/>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -16309,7 +16309,7 @@
       <c r="AM130" t="inlineStr"/>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -16430,7 +16430,7 @@
       <c r="AM131" t="inlineStr"/>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -16551,7 +16551,7 @@
       <c r="AM132" t="inlineStr"/>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -16672,7 +16672,7 @@
       <c r="AM133" t="inlineStr"/>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -16793,7 +16793,7 @@
       <c r="AM134" t="inlineStr"/>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -16914,7 +16914,7 @@
       <c r="AM135" t="inlineStr"/>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -17035,7 +17035,7 @@
       <c r="AM136" t="inlineStr"/>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -17156,7 +17156,7 @@
       <c r="AM137" t="inlineStr"/>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -17277,7 +17277,7 @@
       <c r="AM138" t="inlineStr"/>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -17398,7 +17398,7 @@
       <c r="AM139" t="inlineStr"/>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -17519,7 +17519,7 @@
       <c r="AM140" t="inlineStr"/>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -17640,7 +17640,7 @@
       <c r="AM141" t="inlineStr"/>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17745,7 +17745,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -17761,7 +17761,7 @@
       <c r="AM142" t="inlineStr"/>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -17882,7 +17882,7 @@
       <c r="AM143" t="inlineStr"/>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -18003,7 +18003,7 @@
       <c r="AM144" t="inlineStr"/>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -18124,7 +18124,7 @@
       <c r="AM145" t="inlineStr"/>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -18245,7 +18245,7 @@
       <c r="AM146" t="inlineStr"/>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -18366,7 +18366,7 @@
       <c r="AM147" t="inlineStr"/>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -18487,7 +18487,7 @@
       <c r="AM148" t="inlineStr"/>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -18608,7 +18608,7 @@
       <c r="AM149" t="inlineStr"/>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -18729,7 +18729,7 @@
       <c r="AM150" t="inlineStr"/>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -18850,7 +18850,7 @@
       <c r="AM151" t="inlineStr"/>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -18971,7 +18971,7 @@
       <c r="AM152" t="inlineStr"/>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -19092,7 +19092,7 @@
       <c r="AM153" t="inlineStr"/>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -19213,7 +19213,7 @@
       <c r="AM154" t="inlineStr"/>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -19334,7 +19334,7 @@
       <c r="AM155" t="inlineStr"/>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19439,7 +19439,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -19455,7 +19455,7 @@
       <c r="AM156" t="inlineStr"/>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -19576,7 +19576,7 @@
       <c r="AM157" t="inlineStr"/>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -19697,7 +19697,7 @@
       <c r="AM158" t="inlineStr"/>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -19818,7 +19818,7 @@
       <c r="AM159" t="inlineStr"/>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -19939,7 +19939,7 @@
       <c r="AM160" t="inlineStr"/>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -20060,7 +20060,7 @@
       <c r="AM161" t="inlineStr"/>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -20181,7 +20181,7 @@
       <c r="AM162" t="inlineStr"/>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -20302,7 +20302,7 @@
       <c r="AM163" t="inlineStr"/>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -20423,7 +20423,7 @@
       <c r="AM164" t="inlineStr"/>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20528,7 +20528,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -20544,7 +20544,7 @@
       <c r="AM165" t="inlineStr"/>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -20665,7 +20665,7 @@
       <c r="AM166" t="inlineStr"/>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -20786,7 +20786,7 @@
       <c r="AM167" t="inlineStr"/>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -20907,7 +20907,7 @@
       <c r="AM168" t="inlineStr"/>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -21028,7 +21028,7 @@
       <c r="AM169" t="inlineStr"/>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -21149,7 +21149,7 @@
       <c r="AM170" t="inlineStr"/>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21254,7 +21254,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -21270,7 +21270,7 @@
       <c r="AM171" t="inlineStr"/>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -21391,7 +21391,7 @@
       <c r="AM172" t="inlineStr"/>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -21512,7 +21512,7 @@
       <c r="AM173" t="inlineStr"/>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -21633,7 +21633,7 @@
       <c r="AM174" t="inlineStr"/>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21738,7 +21738,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -21754,7 +21754,7 @@
       <c r="AM175" t="inlineStr"/>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -21875,7 +21875,7 @@
       <c r="AM176" t="inlineStr"/>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -21996,7 +21996,7 @@
       <c r="AM177" t="inlineStr"/>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -22117,7 +22117,7 @@
       <c r="AM178" t="inlineStr"/>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -22238,7 +22238,7 @@
       <c r="AM179" t="inlineStr"/>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -22359,7 +22359,7 @@
       <c r="AM180" t="inlineStr"/>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -22480,7 +22480,7 @@
       <c r="AM181" t="inlineStr"/>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -22601,7 +22601,7 @@
       <c r="AM182" t="inlineStr"/>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -22722,7 +22722,7 @@
       <c r="AM183" t="inlineStr"/>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -22843,7 +22843,7 @@
       <c r="AM184" t="inlineStr"/>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -22964,7 +22964,7 @@
       <c r="AM185" t="inlineStr"/>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23047,7 +23047,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>upper_upscale</t>
+          <t>upscale</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -23069,7 +23069,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -23085,7 +23085,7 @@
       <c r="AM186" t="inlineStr"/>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -23206,7 +23206,7 @@
       <c r="AM187" t="inlineStr"/>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23311,7 +23311,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -23327,7 +23327,7 @@
       <c r="AM188" t="inlineStr"/>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -23448,7 +23448,7 @@
       <c r="AM189" t="inlineStr"/>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -23569,7 +23569,7 @@
       <c r="AM190" t="inlineStr"/>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -23690,7 +23690,7 @@
       <c r="AM191" t="inlineStr"/>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -23811,7 +23811,7 @@
       <c r="AM192" t="inlineStr"/>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -23932,7 +23932,7 @@
       <c r="AM193" t="inlineStr"/>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -24053,7 +24053,7 @@
       <c r="AM194" t="inlineStr"/>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24158,7 +24158,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -24174,7 +24174,7 @@
       <c r="AM195" t="inlineStr"/>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24279,7 +24279,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -24295,7 +24295,7 @@
       <c r="AM196" t="inlineStr"/>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -24416,7 +24416,7 @@
       <c r="AM197" t="inlineStr"/>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -24537,7 +24537,7 @@
       <c r="AM198" t="inlineStr"/>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -24658,7 +24658,7 @@
       <c r="AM199" t="inlineStr"/>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -24763,7 +24763,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -24779,7 +24779,7 @@
       <c r="AM200" t="inlineStr"/>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -24900,7 +24900,7 @@
       <c r="AM201" t="inlineStr"/>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -25021,7 +25021,7 @@
       <c r="AM202" t="inlineStr"/>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -25142,7 +25142,7 @@
       <c r="AM203" t="inlineStr"/>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -25263,7 +25263,7 @@
       <c r="AM204" t="inlineStr"/>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -25384,7 +25384,7 @@
       <c r="AM205" t="inlineStr"/>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25489,7 +25489,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -25505,7 +25505,7 @@
       <c r="AM206" t="inlineStr"/>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -25626,7 +25626,7 @@
       <c r="AM207" t="inlineStr"/>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -25747,7 +25747,7 @@
       <c r="AM208" t="inlineStr"/>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -25868,7 +25868,7 @@
       <c r="AM209" t="inlineStr"/>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -25973,7 +25973,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -25989,7 +25989,7 @@
       <c r="AM210" t="inlineStr"/>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -26110,7 +26110,7 @@
       <c r="AM211" t="inlineStr"/>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -26215,7 +26215,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -26231,7 +26231,7 @@
       <c r="AM212" t="inlineStr"/>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -26352,7 +26352,7 @@
       <c r="AM213" t="inlineStr"/>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -26457,7 +26457,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -26473,7 +26473,7 @@
       <c r="AM214" t="inlineStr"/>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -26594,7 +26594,7 @@
       <c r="AM215" t="inlineStr"/>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -26715,7 +26715,7 @@
       <c r="AM216" t="inlineStr"/>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -26836,7 +26836,7 @@
       <c r="AM217" t="inlineStr"/>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>upper_upscale</t>
+          <t>luxury</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -26957,7 +26957,7 @@
       <c r="AM218" t="inlineStr"/>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -27078,7 +27078,7 @@
       <c r="AM219" t="inlineStr"/>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>upper_upscale</t>
+          <t>upscale</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -27199,7 +27199,7 @@
       <c r="AM220" t="inlineStr"/>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -27304,7 +27304,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -27320,7 +27320,7 @@
       <c r="AM221" t="inlineStr"/>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -27425,7 +27425,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -27441,7 +27441,7 @@
       <c r="AM222" t="inlineStr"/>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -27562,7 +27562,7 @@
       <c r="AM223" t="inlineStr"/>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -27667,7 +27667,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -27683,7 +27683,7 @@
       <c r="AM224" t="inlineStr"/>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -27804,7 +27804,7 @@
       <c r="AM225" t="inlineStr"/>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -27909,7 +27909,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -27925,7 +27925,7 @@
       <c r="AM226" t="inlineStr"/>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -28030,7 +28030,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -28046,7 +28046,7 @@
       <c r="AM227" t="inlineStr"/>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -28151,7 +28151,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -28167,7 +28167,7 @@
       <c r="AM228" t="inlineStr"/>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -28272,7 +28272,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -28288,7 +28288,7 @@
       <c r="AM229" t="inlineStr"/>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -28409,7 +28409,7 @@
       <c r="AM230" t="inlineStr"/>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -28514,7 +28514,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -28530,7 +28530,7 @@
       <c r="AM231" t="inlineStr"/>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -28635,7 +28635,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -28651,7 +28651,7 @@
       <c r="AM232" t="inlineStr"/>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -28756,7 +28756,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -28772,7 +28772,7 @@
       <c r="AM233" t="inlineStr"/>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -28877,7 +28877,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -28893,7 +28893,7 @@
       <c r="AM234" t="inlineStr"/>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -29014,7 +29014,7 @@
       <c r="AM235" t="inlineStr"/>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -29119,7 +29119,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -29135,7 +29135,7 @@
       <c r="AM236" t="inlineStr"/>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -29240,7 +29240,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -29256,7 +29256,7 @@
       <c r="AM237" t="inlineStr"/>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -29361,7 +29361,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -29377,7 +29377,7 @@
       <c r="AM238" t="inlineStr"/>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -29482,7 +29482,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -29498,7 +29498,7 @@
       <c r="AM239" t="inlineStr"/>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -29619,7 +29619,7 @@
       <c r="AM240" t="inlineStr"/>
       <c r="AN240" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -29724,7 +29724,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -29740,7 +29740,7 @@
       <c r="AM241" t="inlineStr"/>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -29845,7 +29845,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -29861,7 +29861,7 @@
       <c r="AM242" t="inlineStr"/>
       <c r="AN242" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -29966,7 +29966,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -29982,7 +29982,7 @@
       <c r="AM243" t="inlineStr"/>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -30087,7 +30087,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -30103,7 +30103,7 @@
       <c r="AM244" t="inlineStr"/>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -30224,7 +30224,7 @@
       <c r="AM245" t="inlineStr"/>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -30345,7 +30345,7 @@
       <c r="AM246" t="inlineStr"/>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -30450,7 +30450,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -30466,7 +30466,7 @@
       <c r="AM247" t="inlineStr"/>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
@@ -30587,7 +30587,7 @@
       <c r="AM248" t="inlineStr"/>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -30708,7 +30708,7 @@
       <c r="AM249" t="inlineStr"/>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -30829,7 +30829,7 @@
       <c r="AM250" t="inlineStr"/>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -30950,7 +30950,7 @@
       <c r="AM251" t="inlineStr"/>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
@@ -31055,7 +31055,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -31071,7 +31071,7 @@
       <c r="AM252" t="inlineStr"/>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -31176,7 +31176,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -31192,7 +31192,7 @@
       <c r="AM253" t="inlineStr"/>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>upscale</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -31313,7 +31313,7 @@
       <c r="AM254" t="inlineStr"/>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -31418,7 +31418,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -31434,7 +31434,7 @@
       <c r="AM255" t="inlineStr"/>
       <c r="AN255" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -31539,7 +31539,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -31555,7 +31555,7 @@
       <c r="AM256" t="inlineStr"/>
       <c r="AN256" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -31660,7 +31660,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -31676,7 +31676,7 @@
       <c r="AM257" t="inlineStr"/>
       <c r="AN257" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -31797,7 +31797,7 @@
       <c r="AM258" t="inlineStr"/>
       <c r="AN258" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -31902,7 +31902,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -31918,7 +31918,7 @@
       <c r="AM259" t="inlineStr"/>
       <c r="AN259" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
@@ -32023,7 +32023,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -32039,7 +32039,7 @@
       <c r="AM260" t="inlineStr"/>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -32160,7 +32160,7 @@
       <c r="AM261" t="inlineStr"/>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -32281,7 +32281,7 @@
       <c r="AM262" t="inlineStr"/>
       <c r="AN262" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -32402,7 +32402,7 @@
       <c r="AM263" t="inlineStr"/>
       <c r="AN263" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -32523,7 +32523,7 @@
       <c r="AM264" t="inlineStr"/>
       <c r="AN264" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -32644,7 +32644,7 @@
       <c r="AM265" t="inlineStr"/>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
@@ -32727,7 +32727,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>upper_upscale</t>
+          <t>upscale</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -32749,7 +32749,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -32765,7 +32765,7 @@
       <c r="AM266" t="inlineStr"/>
       <c r="AN266" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -32886,7 +32886,7 @@
       <c r="AM267" t="inlineStr"/>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -33007,7 +33007,7 @@
       <c r="AM268" t="inlineStr"/>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>upscale</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -33112,7 +33112,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -33128,7 +33128,7 @@
       <c r="AM269" t="inlineStr"/>
       <c r="AN269" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -33249,7 +33249,7 @@
       <c r="AM270" t="inlineStr"/>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -33370,7 +33370,7 @@
       <c r="AM271" t="inlineStr"/>
       <c r="AN271" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO271" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -33491,7 +33491,7 @@
       <c r="AM272" t="inlineStr"/>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
@@ -33596,7 +33596,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -33612,7 +33612,7 @@
       <c r="AM273" t="inlineStr"/>
       <c r="AN273" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO273" t="inlineStr">
@@ -33717,7 +33717,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -33733,7 +33733,7 @@
       <c r="AM274" t="inlineStr"/>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -33838,7 +33838,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -33854,7 +33854,7 @@
       <c r="AM275" t="inlineStr"/>
       <c r="AN275" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO275" t="inlineStr">
@@ -33959,7 +33959,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -33975,7 +33975,7 @@
       <c r="AM276" t="inlineStr"/>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -34096,7 +34096,7 @@
       <c r="AM277" t="inlineStr"/>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -34201,7 +34201,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -34217,7 +34217,7 @@
       <c r="AM278" t="inlineStr"/>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -34322,7 +34322,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -34338,7 +34338,7 @@
       <c r="AM279" t="inlineStr"/>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -34443,7 +34443,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -34459,7 +34459,7 @@
       <c r="AM280" t="inlineStr"/>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
@@ -34564,7 +34564,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -34580,7 +34580,7 @@
       <c r="AM281" t="inlineStr"/>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
@@ -34685,7 +34685,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -34701,7 +34701,7 @@
       <c r="AM282" t="inlineStr"/>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -34822,7 +34822,7 @@
       <c r="AM283" t="inlineStr"/>
       <c r="AN283" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">
@@ -34927,7 +34927,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
@@ -34943,7 +34943,7 @@
       <c r="AM284" t="inlineStr"/>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -35048,7 +35048,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -35064,7 +35064,7 @@
       <c r="AM285" t="inlineStr"/>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -35185,7 +35185,7 @@
       <c r="AM286" t="inlineStr"/>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -35306,7 +35306,7 @@
       <c r="AM287" t="inlineStr"/>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -35411,7 +35411,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -35427,7 +35427,7 @@
       <c r="AM288" t="inlineStr"/>
       <c r="AN288" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -35532,7 +35532,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -35548,7 +35548,7 @@
       <c r="AM289" t="inlineStr"/>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
@@ -35653,7 +35653,7 @@
       </c>
       <c r="AJ290" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK290" t="inlineStr">
@@ -35669,7 +35669,7 @@
       <c r="AM290" t="inlineStr"/>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -35790,7 +35790,7 @@
       <c r="AM291" t="inlineStr"/>
       <c r="AN291" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO291" t="inlineStr">
@@ -35895,7 +35895,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -35911,7 +35911,7 @@
       <c r="AM292" t="inlineStr"/>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
@@ -36016,7 +36016,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -36032,7 +36032,7 @@
       <c r="AM293" t="inlineStr"/>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
@@ -36137,7 +36137,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -36153,7 +36153,7 @@
       <c r="AM294" t="inlineStr"/>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -36258,7 +36258,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -36274,7 +36274,7 @@
       <c r="AM295" t="inlineStr"/>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
@@ -36379,7 +36379,7 @@
       </c>
       <c r="AJ296" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK296" t="inlineStr">
@@ -36395,7 +36395,7 @@
       <c r="AM296" t="inlineStr"/>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -36500,7 +36500,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -36516,7 +36516,7 @@
       <c r="AM297" t="inlineStr"/>
       <c r="AN297" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -36637,7 +36637,7 @@
       <c r="AM298" t="inlineStr"/>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -36742,7 +36742,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -36758,7 +36758,7 @@
       <c r="AM299" t="inlineStr"/>
       <c r="AN299" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -36863,7 +36863,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -36879,7 +36879,7 @@
       <c r="AM300" t="inlineStr"/>
       <c r="AN300" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -36984,7 +36984,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -37000,7 +37000,7 @@
       <c r="AM301" t="inlineStr"/>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="AJ302" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK302" t="inlineStr">
@@ -37121,7 +37121,7 @@
       <c r="AM302" t="inlineStr"/>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -37242,7 +37242,7 @@
       <c r="AM303" t="inlineStr"/>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
@@ -37347,7 +37347,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -37363,7 +37363,7 @@
       <c r="AM304" t="inlineStr"/>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -37484,7 +37484,7 @@
       <c r="AM305" t="inlineStr"/>
       <c r="AN305" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO305" t="inlineStr">
@@ -37589,7 +37589,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -37605,7 +37605,7 @@
       <c r="AM306" t="inlineStr"/>
       <c r="AN306" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -37726,7 +37726,7 @@
       <c r="AM307" t="inlineStr"/>
       <c r="AN307" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO307" t="inlineStr">
@@ -37831,7 +37831,7 @@
       </c>
       <c r="AJ308" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK308" t="inlineStr">
@@ -37847,7 +37847,7 @@
       <c r="AM308" t="inlineStr"/>
       <c r="AN308" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO308" t="inlineStr">
@@ -37952,7 +37952,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -37968,7 +37968,7 @@
       <c r="AM309" t="inlineStr"/>
       <c r="AN309" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
@@ -38073,7 +38073,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -38089,7 +38089,7 @@
       <c r="AM310" t="inlineStr"/>
       <c r="AN310" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -38210,7 +38210,7 @@
       <c r="AM311" t="inlineStr"/>
       <c r="AN311" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -38315,7 +38315,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -38331,7 +38331,7 @@
       <c r="AM312" t="inlineStr"/>
       <c r="AN312" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -38436,7 +38436,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -38452,7 +38452,7 @@
       <c r="AM313" t="inlineStr"/>
       <c r="AN313" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO313" t="inlineStr">
@@ -38557,7 +38557,7 @@
       </c>
       <c r="AJ314" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK314" t="inlineStr">
@@ -38573,7 +38573,7 @@
       <c r="AM314" t="inlineStr"/>
       <c r="AN314" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -38694,7 +38694,7 @@
       <c r="AM315" t="inlineStr"/>
       <c r="AN315" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO315" t="inlineStr">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="AJ316" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK316" t="inlineStr">
@@ -38815,7 +38815,7 @@
       <c r="AM316" t="inlineStr"/>
       <c r="AN316" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO316" t="inlineStr">
@@ -38920,7 +38920,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -38936,7 +38936,7 @@
       <c r="AM317" t="inlineStr"/>
       <c r="AN317" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="AJ318" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK318" t="inlineStr">
@@ -39057,7 +39057,7 @@
       <c r="AM318" t="inlineStr"/>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -39178,7 +39178,7 @@
       <c r="AM319" t="inlineStr"/>
       <c r="AN319" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="AJ320" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK320" t="inlineStr">
@@ -39299,7 +39299,7 @@
       <c r="AM320" t="inlineStr"/>
       <c r="AN320" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO320" t="inlineStr">
@@ -39404,7 +39404,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -39420,7 +39420,7 @@
       <c r="AM321" t="inlineStr"/>
       <c r="AN321" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO321" t="inlineStr">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="AJ322" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK322" t="inlineStr">
@@ -39541,7 +39541,7 @@
       <c r="AM322" t="inlineStr"/>
       <c r="AN322" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
@@ -39646,7 +39646,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -39662,7 +39662,7 @@
       <c r="AM323" t="inlineStr"/>
       <c r="AN323" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
@@ -39767,7 +39767,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -39783,7 +39783,7 @@
       <c r="AM324" t="inlineStr"/>
       <c r="AN324" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO324" t="inlineStr">
@@ -39888,7 +39888,7 @@
       </c>
       <c r="AJ325" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK325" t="inlineStr">
@@ -39904,7 +39904,7 @@
       <c r="AM325" t="inlineStr"/>
       <c r="AN325" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
@@ -40009,7 +40009,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -40025,7 +40025,7 @@
       <c r="AM326" t="inlineStr"/>
       <c r="AN326" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO326" t="inlineStr">
@@ -40130,7 +40130,7 @@
       </c>
       <c r="AJ327" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK327" t="inlineStr">
@@ -40146,7 +40146,7 @@
       <c r="AM327" t="inlineStr"/>
       <c r="AN327" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO327" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="AJ328" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK328" t="inlineStr">
@@ -40267,7 +40267,7 @@
       <c r="AM328" t="inlineStr"/>
       <c r="AN328" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO328" t="inlineStr">
@@ -40372,7 +40372,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -40388,7 +40388,7 @@
       <c r="AM329" t="inlineStr"/>
       <c r="AN329" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO329" t="inlineStr">
@@ -40493,7 +40493,7 @@
       </c>
       <c r="AJ330" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK330" t="inlineStr">
@@ -40509,7 +40509,7 @@
       <c r="AM330" t="inlineStr"/>
       <c r="AN330" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO330" t="inlineStr">
@@ -40614,7 +40614,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -40630,7 +40630,7 @@
       <c r="AM331" t="inlineStr"/>
       <c r="AN331" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO331" t="inlineStr">
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AJ332" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK332" t="inlineStr">
@@ -40751,7 +40751,7 @@
       <c r="AM332" t="inlineStr"/>
       <c r="AN332" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO332" t="inlineStr">
@@ -40856,7 +40856,7 @@
       </c>
       <c r="AJ333" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK333" t="inlineStr">
@@ -40872,7 +40872,7 @@
       <c r="AM333" t="inlineStr"/>
       <c r="AN333" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO333" t="inlineStr">
@@ -40977,7 +40977,7 @@
       </c>
       <c r="AJ334" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK334" t="inlineStr">
@@ -40993,7 +40993,7 @@
       <c r="AM334" t="inlineStr"/>
       <c r="AN334" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO334" t="inlineStr">
@@ -41098,7 +41098,7 @@
       </c>
       <c r="AJ335" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK335" t="inlineStr">
@@ -41114,7 +41114,7 @@
       <c r="AM335" t="inlineStr"/>
       <c r="AN335" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO335" t="inlineStr">
@@ -41219,7 +41219,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -41235,7 +41235,7 @@
       <c r="AM336" t="inlineStr"/>
       <c r="AN336" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO336" t="inlineStr">
@@ -41340,7 +41340,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -41356,7 +41356,7 @@
       <c r="AM337" t="inlineStr"/>
       <c r="AN337" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO337" t="inlineStr">
@@ -41461,7 +41461,7 @@
       </c>
       <c r="AJ338" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK338" t="inlineStr">
@@ -41477,7 +41477,7 @@
       <c r="AM338" t="inlineStr"/>
       <c r="AN338" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -41582,7 +41582,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -41598,7 +41598,7 @@
       <c r="AM339" t="inlineStr"/>
       <c r="AN339" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
@@ -41703,7 +41703,7 @@
       </c>
       <c r="AJ340" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK340" t="inlineStr">
@@ -41719,7 +41719,7 @@
       <c r="AM340" t="inlineStr"/>
       <c r="AN340" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO340" t="inlineStr">
@@ -41824,7 +41824,7 @@
       </c>
       <c r="AJ341" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK341" t="inlineStr">
@@ -41840,7 +41840,7 @@
       <c r="AM341" t="inlineStr"/>
       <c r="AN341" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
@@ -41945,7 +41945,7 @@
       </c>
       <c r="AJ342" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK342" t="inlineStr">
@@ -41961,7 +41961,7 @@
       <c r="AM342" t="inlineStr"/>
       <c r="AN342" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO342" t="inlineStr">
@@ -42066,7 +42066,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -42082,7 +42082,7 @@
       <c r="AM343" t="inlineStr"/>
       <c r="AN343" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AJ344" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK344" t="inlineStr">
@@ -42203,7 +42203,7 @@
       <c r="AM344" t="inlineStr"/>
       <c r="AN344" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO344" t="inlineStr">
@@ -42308,7 +42308,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -42324,7 +42324,7 @@
       <c r="AM345" t="inlineStr"/>
       <c r="AN345" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
@@ -42445,7 +42445,7 @@
       <c r="AM346" t="inlineStr"/>
       <c r="AN346" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO346" t="inlineStr">
@@ -42550,7 +42550,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -42566,7 +42566,7 @@
       <c r="AM347" t="inlineStr"/>
       <c r="AN347" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO347" t="inlineStr">
@@ -42671,7 +42671,7 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
@@ -42687,7 +42687,7 @@
       <c r="AM348" t="inlineStr"/>
       <c r="AN348" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO348" t="inlineStr">
@@ -42792,7 +42792,7 @@
       </c>
       <c r="AJ349" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK349" t="inlineStr">
@@ -42808,7 +42808,7 @@
       <c r="AM349" t="inlineStr"/>
       <c r="AN349" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO349" t="inlineStr">
@@ -42913,7 +42913,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -42929,7 +42929,7 @@
       <c r="AM350" t="inlineStr"/>
       <c r="AN350" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO350" t="inlineStr">
@@ -43034,7 +43034,7 @@
       </c>
       <c r="AJ351" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK351" t="inlineStr">
@@ -43050,7 +43050,7 @@
       <c r="AM351" t="inlineStr"/>
       <c r="AN351" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO351" t="inlineStr">
@@ -43155,7 +43155,7 @@
       </c>
       <c r="AJ352" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK352" t="inlineStr">
@@ -43171,7 +43171,7 @@
       <c r="AM352" t="inlineStr"/>
       <c r="AN352" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO352" t="inlineStr">
@@ -43276,7 +43276,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -43292,7 +43292,7 @@
       <c r="AM353" t="inlineStr"/>
       <c r="AN353" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO353" t="inlineStr">
@@ -43397,7 +43397,7 @@
       </c>
       <c r="AJ354" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK354" t="inlineStr">
@@ -43413,7 +43413,7 @@
       <c r="AM354" t="inlineStr"/>
       <c r="AN354" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO354" t="inlineStr">
@@ -43518,7 +43518,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -43534,7 +43534,7 @@
       <c r="AM355" t="inlineStr"/>
       <c r="AN355" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO355" t="inlineStr">
@@ -43639,7 +43639,7 @@
       </c>
       <c r="AJ356" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK356" t="inlineStr">
@@ -43655,7 +43655,7 @@
       <c r="AM356" t="inlineStr"/>
       <c r="AN356" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO356" t="inlineStr">
@@ -43760,7 +43760,7 @@
       </c>
       <c r="AJ357" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK357" t="inlineStr">
@@ -43776,7 +43776,7 @@
       <c r="AM357" t="inlineStr"/>
       <c r="AN357" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO357" t="inlineStr">
@@ -43881,7 +43881,7 @@
       </c>
       <c r="AJ358" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK358" t="inlineStr">
@@ -43897,7 +43897,7 @@
       <c r="AM358" t="inlineStr"/>
       <c r="AN358" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO358" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>upper_midscale</t>
+          <t>midscale</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -44002,7 +44002,7 @@
       </c>
       <c r="AJ359" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK359" t="inlineStr">
@@ -44018,7 +44018,7 @@
       <c r="AM359" t="inlineStr"/>
       <c r="AN359" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO359" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="AJ360" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK360" t="inlineStr">
@@ -44139,7 +44139,7 @@
       <c r="AM360" t="inlineStr"/>
       <c r="AN360" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO360" t="inlineStr">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -44260,7 +44260,7 @@
       <c r="AM361" t="inlineStr"/>
       <c r="AN361" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO361" t="inlineStr">
@@ -44365,7 +44365,7 @@
       </c>
       <c r="AJ362" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK362" t="inlineStr">
@@ -44381,7 +44381,7 @@
       <c r="AM362" t="inlineStr"/>
       <c r="AN362" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO362" t="inlineStr">
@@ -44486,7 +44486,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -44502,7 +44502,7 @@
       <c r="AM363" t="inlineStr"/>
       <c r="AN363" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO363" t="inlineStr">
@@ -44607,7 +44607,7 @@
       </c>
       <c r="AJ364" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK364" t="inlineStr">
@@ -44623,7 +44623,7 @@
       <c r="AM364" t="inlineStr"/>
       <c r="AN364" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO364" t="inlineStr">
@@ -44728,7 +44728,7 @@
       </c>
       <c r="AJ365" t="inlineStr">
         <is>
-          <t>batch_8c1ba6a7e5264098</t>
+          <t>batch_2e8f5425de7c49e5</t>
         </is>
       </c>
       <c r="AK365" t="inlineStr">
@@ -44744,7 +44744,7 @@
       <c r="AM365" t="inlineStr"/>
       <c r="AN365" t="inlineStr">
         <is>
-          <t>2026-05-14T03:38:37+00:00</t>
+          <t>2026-05-14T03:50:20+00:00</t>
         </is>
       </c>
       <c r="AO365" t="inlineStr">
@@ -46421,7 +46421,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:45:44+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-14T03:51:00+00:00. Normalization version: v1.0.</t>
         </is>
       </c>
     </row>
